--- a/output/roomself_excel/518.xlsx
+++ b/output/roomself_excel/518.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>95100</v>
+        <v>146294</v>
       </c>
       <c r="D2" t="n">
-        <v>2468</v>
+        <v>3104</v>
       </c>
       <c r="E2" t="n">
-        <v>385</v>
+        <v>346</v>
       </c>
       <c r="F2" t="n">
-        <v>331</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>127795</v>
+        <v>1011212</v>
       </c>
       <c r="D3" t="n">
-        <v>2896</v>
+        <v>11232</v>
       </c>
       <c r="E3" t="n">
-        <v>652</v>
+        <v>1007</v>
       </c>
       <c r="F3" t="n">
-        <v>364</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>116901</v>
+        <v>244766</v>
       </c>
       <c r="D4" t="n">
-        <v>2792</v>
+        <v>3984</v>
       </c>
       <c r="E4" t="n">
-        <v>279</v>
+        <v>503</v>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>499075</v>
+        <v>127795</v>
       </c>
       <c r="D5" t="n">
-        <v>8432</v>
+        <v>2896</v>
       </c>
       <c r="E5" t="n">
-        <v>1131</v>
+        <v>305</v>
       </c>
       <c r="F5" t="n">
-        <v>970</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
@@ -554,17 +554,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>47838</v>
+        <v>116901</v>
       </c>
       <c r="D6" t="n">
-        <v>1756</v>
+        <v>2792</v>
       </c>
       <c r="E6" t="n">
-        <v>238</v>
+        <v>279</v>
       </c>
       <c r="F6" t="n">
         <v>31</v>
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>30504</v>
+        <v>96432</v>
       </c>
       <c r="D7" t="n">
-        <v>1452</v>
+        <v>2488</v>
       </c>
       <c r="E7" t="n">
-        <v>270</v>
+        <v>294</v>
       </c>
       <c r="F7" t="n">
-        <v>193</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>48076</v>
+        <v>181583</v>
       </c>
       <c r="D8" t="n">
-        <v>1760</v>
+        <v>3884</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>31086</v>
+        <v>225688</v>
       </c>
       <c r="D9" t="n">
-        <v>1456</v>
+        <v>4084</v>
       </c>
       <c r="E9" t="n">
-        <v>202</v>
+        <v>279</v>
       </c>
       <c r="F9" t="n">
-        <v>31</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>172500</v>
+        <v>48076</v>
       </c>
       <c r="D10" t="n">
-        <v>3500</v>
+        <v>1760</v>
       </c>
       <c r="E10" t="n">
-        <v>606</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23552</v>
+        <v>31086</v>
       </c>
       <c r="D11" t="n">
-        <v>1248</v>
+        <v>1456</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30880</v>
+        <v>115422</v>
       </c>
       <c r="D12" t="n">
-        <v>1412</v>
+        <v>3596</v>
       </c>
       <c r="E12" t="n">
-        <v>487</v>
+        <v>345</v>
       </c>
       <c r="F12" t="n">
-        <v>16</v>
+        <v>288</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>157248</v>
+        <v>19995</v>
       </c>
       <c r="D13" t="n">
-        <v>3196</v>
+        <v>1136</v>
       </c>
       <c r="E13" t="n">
-        <v>525</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>31089</v>
+        <v>22720</v>
       </c>
       <c r="D14" t="n">
-        <v>1480</v>
+        <v>1208</v>
       </c>
       <c r="E14" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -752,20 +752,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>89652</v>
+        <v>18590</v>
       </c>
       <c r="D15" t="n">
-        <v>2452</v>
+        <v>1092</v>
       </c>
       <c r="E15" t="n">
-        <v>372</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>115422</v>
+        <v>108015</v>
       </c>
       <c r="D16" t="n">
-        <v>3596</v>
+        <v>3324</v>
       </c>
       <c r="E16" t="n">
-        <v>345</v>
+        <v>128</v>
       </c>
       <c r="F16" t="n">
-        <v>288</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -796,17 +796,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>96432</v>
+        <v>31089</v>
       </c>
       <c r="D17" t="n">
-        <v>2488</v>
+        <v>1480</v>
       </c>
       <c r="E17" t="n">
-        <v>294</v>
+        <v>241</v>
       </c>
       <c r="F17" t="n">
         <v>31</v>
@@ -818,14 +818,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>19995</v>
+        <v>94472</v>
       </c>
       <c r="D18" t="n">
-        <v>1136</v>
+        <v>2532</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -840,20 +840,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1105684</v>
+        <v>15066</v>
       </c>
       <c r="D19" t="n">
-        <v>12800</v>
+        <v>1068</v>
       </c>
       <c r="E19" t="n">
-        <v>1645</v>
+        <v>186</v>
       </c>
       <c r="F19" t="n">
-        <v>1582</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20">
@@ -862,20 +862,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22720</v>
+        <v>95100</v>
       </c>
       <c r="D20" t="n">
-        <v>1208</v>
+        <v>2468</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>331</v>
       </c>
     </row>
     <row r="21">
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>76298</v>
+        <v>47838</v>
       </c>
       <c r="D21" t="n">
-        <v>2412</v>
+        <v>1756</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22">
@@ -906,20 +906,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>44173</v>
+        <v>23552</v>
       </c>
       <c r="D22" t="n">
-        <v>1736</v>
+        <v>1248</v>
       </c>
       <c r="E22" t="n">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -932,16 +932,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>20253</v>
+        <v>30880</v>
       </c>
       <c r="D23" t="n">
-        <v>1144</v>
+        <v>1412</v>
       </c>
       <c r="E23" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -950,20 +950,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>181583</v>
+        <v>76298</v>
       </c>
       <c r="D24" t="n">
-        <v>3884</v>
+        <v>2412</v>
       </c>
       <c r="E24" t="n">
-        <v>231</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -976,16 +976,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>29756</v>
+        <v>20253</v>
       </c>
       <c r="D25" t="n">
-        <v>1460</v>
+        <v>1144</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26">
@@ -994,20 +994,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>15066</v>
+        <v>29756</v>
       </c>
       <c r="D26" t="n">
-        <v>1068</v>
+        <v>1460</v>
       </c>
       <c r="E26" t="n">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1016,20 +1016,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>18590</v>
+        <v>21252</v>
       </c>
       <c r="D27" t="n">
-        <v>1092</v>
+        <v>1168</v>
       </c>
       <c r="E27" t="n">
-        <v>574</v>
+        <v>138</v>
       </c>
       <c r="F27" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28">
@@ -1038,20 +1038,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>154832</v>
+        <v>172500</v>
       </c>
       <c r="D28" t="n">
-        <v>3200</v>
+        <v>3500</v>
       </c>
       <c r="E28" t="n">
-        <v>388</v>
+        <v>606</v>
       </c>
       <c r="F28" t="n">
-        <v>345</v>
+        <v>331</v>
       </c>
     </row>
     <row r="29">
@@ -1060,20 +1060,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>21252</v>
+        <v>30504</v>
       </c>
       <c r="D29" t="n">
-        <v>1168</v>
+        <v>1452</v>
       </c>
       <c r="E29" t="n">
-        <v>138</v>
+        <v>270</v>
       </c>
       <c r="F29" t="n">
-        <v>31</v>
+        <v>193</v>
       </c>
     </row>
     <row r="30">
@@ -1082,20 +1082,86 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>225688</v>
+        <v>157248</v>
       </c>
       <c r="D30" t="n">
-        <v>4084</v>
+        <v>3196</v>
       </c>
       <c r="E30" t="n">
-        <v>279</v>
+        <v>389</v>
       </c>
       <c r="F30" t="n">
-        <v>201</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>89652</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2452</v>
+      </c>
+      <c r="E31" t="n">
+        <v>372</v>
+      </c>
+      <c r="F31" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>44173</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1736</v>
+      </c>
+      <c r="E32" t="n">
+        <v>271</v>
+      </c>
+      <c r="F32" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>154832</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3200</v>
+      </c>
+      <c r="E33" t="n">
+        <v>372</v>
+      </c>
+      <c r="F33" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/518.xlsx
+++ b/output/roomself_excel/518.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>3104</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>346</v>
       </c>
-      <c r="F2" t="n">
-        <v>31</v>
-      </c>
+      <c r="G2" t="n">
+        <v>31</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +525,27 @@
       <c r="D3" t="n">
         <v>11232</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>1007</v>
       </c>
-      <c r="F3" t="n">
-        <v>31</v>
+      <c r="G3" t="n">
+        <v>31</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>943</v>
+      </c>
+      <c r="J3" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -519,12 +563,20 @@
       <c r="D4" t="n">
         <v>3984</v>
       </c>
-      <c r="E4" t="n">
-        <v>503</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>128</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="G4" t="n">
+        <v>31</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +593,20 @@
       <c r="D5" t="n">
         <v>2896</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>305</v>
       </c>
-      <c r="F5" t="n">
-        <v>31</v>
-      </c>
+      <c r="G5" t="n">
+        <v>31</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +623,20 @@
       <c r="D6" t="n">
         <v>2792</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>279</v>
       </c>
-      <c r="F6" t="n">
-        <v>31</v>
-      </c>
+      <c r="G6" t="n">
+        <v>31</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +653,20 @@
       <c r="D7" t="n">
         <v>2488</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>294</v>
       </c>
-      <c r="F7" t="n">
-        <v>31</v>
-      </c>
+      <c r="G7" t="n">
+        <v>31</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +683,20 @@
       <c r="D8" t="n">
         <v>3884</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>231</v>
       </c>
-      <c r="F8" t="n">
-        <v>31</v>
-      </c>
+      <c r="G8" t="n">
+        <v>31</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,11 +713,27 @@
       <c r="D9" t="n">
         <v>4084</v>
       </c>
-      <c r="E9" t="n">
-        <v>279</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>201</v>
+        <v>263</v>
+      </c>
+      <c r="G9" t="n">
+        <v>31</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>604</v>
+      </c>
+      <c r="J9" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="10">
@@ -651,12 +751,12 @@
       <c r="D10" t="n">
         <v>1760</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +773,20 @@
       <c r="D11" t="n">
         <v>1456</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>202</v>
       </c>
-      <c r="F11" t="n">
-        <v>31</v>
-      </c>
+      <c r="G11" t="n">
+        <v>31</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,11 +803,27 @@
       <c r="D12" t="n">
         <v>3596</v>
       </c>
-      <c r="E12" t="n">
-        <v>345</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>288</v>
+        <v>298</v>
+      </c>
+      <c r="G12" t="n">
+        <v>31</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>241</v>
+      </c>
+      <c r="J12" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="13">
@@ -717,12 +841,12 @@
       <c r="D13" t="n">
         <v>1136</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +863,12 @@
       <c r="D14" t="n">
         <v>1208</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +885,12 @@
       <c r="D15" t="n">
         <v>1092</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +907,12 @@
       <c r="D16" t="n">
         <v>3324</v>
       </c>
-      <c r="E16" t="n">
-        <v>128</v>
-      </c>
-      <c r="F16" t="n">
-        <v>15</v>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +929,20 @@
       <c r="D17" t="n">
         <v>1480</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
         <v>241</v>
       </c>
-      <c r="F17" t="n">
-        <v>31</v>
-      </c>
+      <c r="G17" t="n">
+        <v>31</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +959,12 @@
       <c r="D18" t="n">
         <v>2532</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +981,20 @@
       <c r="D19" t="n">
         <v>1068</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
         <v>186</v>
       </c>
-      <c r="F19" t="n">
-        <v>31</v>
-      </c>
+      <c r="G19" t="n">
+        <v>31</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,11 +1011,27 @@
       <c r="D20" t="n">
         <v>2468</v>
       </c>
-      <c r="E20" t="n">
-        <v>385</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F20" t="n">
-        <v>331</v>
+        <v>317</v>
+      </c>
+      <c r="G20" t="n">
+        <v>31</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>299</v>
+      </c>
+      <c r="J20" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="21">
@@ -893,12 +1049,20 @@
       <c r="D21" t="n">
         <v>1756</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
         <v>238</v>
       </c>
-      <c r="F21" t="n">
-        <v>31</v>
-      </c>
+      <c r="G21" t="n">
+        <v>31</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +1079,12 @@
       <c r="D22" t="n">
         <v>1248</v>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +1101,12 @@
       <c r="D23" t="n">
         <v>1412</v>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,12 +1123,12 @@
       <c r="D24" t="n">
         <v>2412</v>
       </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,12 +1145,20 @@
       <c r="D25" t="n">
         <v>1144</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
         <v>129</v>
       </c>
-      <c r="F25" t="n">
-        <v>31</v>
-      </c>
+      <c r="G25" t="n">
+        <v>31</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1003,12 +1175,12 @@
       <c r="D26" t="n">
         <v>1460</v>
       </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1025,12 +1197,20 @@
       <c r="D27" t="n">
         <v>1168</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
         <v>138</v>
       </c>
-      <c r="F27" t="n">
-        <v>31</v>
-      </c>
+      <c r="G27" t="n">
+        <v>31</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1047,11 +1227,27 @@
       <c r="D28" t="n">
         <v>3500</v>
       </c>
-      <c r="E28" t="n">
-        <v>606</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F28" t="n">
-        <v>331</v>
+        <v>575</v>
+      </c>
+      <c r="G28" t="n">
+        <v>31</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>300</v>
+      </c>
+      <c r="J28" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="29">
@@ -1069,11 +1265,27 @@
       <c r="D29" t="n">
         <v>1452</v>
       </c>
-      <c r="E29" t="n">
-        <v>270</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F29" t="n">
-        <v>193</v>
+        <v>161</v>
+      </c>
+      <c r="G29" t="n">
+        <v>31</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>201</v>
+      </c>
+      <c r="J29" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="30">
@@ -1091,12 +1303,20 @@
       <c r="D30" t="n">
         <v>3196</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
         <v>389</v>
       </c>
-      <c r="F30" t="n">
-        <v>31</v>
-      </c>
+      <c r="G30" t="n">
+        <v>31</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1113,12 +1333,20 @@
       <c r="D31" t="n">
         <v>2452</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>372</v>
       </c>
-      <c r="F31" t="n">
-        <v>31</v>
-      </c>
+      <c r="G31" t="n">
+        <v>31</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1135,12 +1363,20 @@
       <c r="D32" t="n">
         <v>1736</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
         <v>271</v>
       </c>
-      <c r="F32" t="n">
-        <v>31</v>
-      </c>
+      <c r="G32" t="n">
+        <v>31</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1157,12 +1393,20 @@
       <c r="D33" t="n">
         <v>3200</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
         <v>372</v>
       </c>
-      <c r="F33" t="n">
-        <v>31</v>
-      </c>
+      <c r="G33" t="n">
+        <v>31</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/518.xlsx
+++ b/output/roomself_excel/518.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:R33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,46 @@
           <t>ExtWallWidth_2</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -509,6 +549,26 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>168</v>
+      </c>
+      <c r="N2" t="n">
+        <v>31</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -547,6 +607,38 @@
       <c r="J3" t="n">
         <v>30</v>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>789</v>
+      </c>
+      <c r="N3" t="n">
+        <v>31</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>336</v>
+      </c>
+      <c r="R3" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -577,6 +669,26 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>344</v>
+      </c>
+      <c r="N4" t="n">
+        <v>31</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -607,6 +719,26 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>176</v>
+      </c>
+      <c r="N5" t="n">
+        <v>31</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -637,6 +769,26 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>176</v>
+      </c>
+      <c r="N6" t="n">
+        <v>31</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -667,6 +819,26 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>181</v>
+      </c>
+      <c r="N7" t="n">
+        <v>31</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -697,6 +869,26 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>178</v>
+      </c>
+      <c r="N8" t="n">
+        <v>31</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -735,6 +927,26 @@
       <c r="J9" t="n">
         <v>30</v>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>357</v>
+      </c>
+      <c r="N9" t="n">
+        <v>30</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -757,6 +969,14 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -787,6 +1007,14 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -825,6 +1053,14 @@
       <c r="J12" t="n">
         <v>31</v>
       </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -847,6 +1083,14 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -869,6 +1113,14 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -891,6 +1143,14 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -913,6 +1173,14 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -943,6 +1211,38 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>85</v>
+      </c>
+      <c r="N17" t="n">
+        <v>31</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>57</v>
+      </c>
+      <c r="R17" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -965,6 +1265,14 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -995,6 +1303,26 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>93</v>
+      </c>
+      <c r="N19" t="n">
+        <v>31</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1033,6 +1361,38 @@
       <c r="J20" t="n">
         <v>31</v>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>130</v>
+      </c>
+      <c r="N20" t="n">
+        <v>31</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>88</v>
+      </c>
+      <c r="R20" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1063,6 +1423,38 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>74</v>
+      </c>
+      <c r="N21" t="n">
+        <v>31</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>144</v>
+      </c>
+      <c r="R21" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1085,6 +1477,14 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1107,6 +1507,14 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1129,6 +1537,14 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1159,6 +1575,14 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1181,6 +1605,14 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1211,6 +1643,14 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1249,6 +1689,26 @@
       <c r="J28" t="n">
         <v>31</v>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>241</v>
+      </c>
+      <c r="N28" t="n">
+        <v>31</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1287,6 +1747,26 @@
       <c r="J29" t="n">
         <v>31</v>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>84</v>
+      </c>
+      <c r="N29" t="n">
+        <v>31</v>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1317,6 +1797,38 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>94</v>
+      </c>
+      <c r="N30" t="n">
+        <v>31</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>119</v>
+      </c>
+      <c r="R30" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1347,6 +1859,38 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>173</v>
+      </c>
+      <c r="N31" t="n">
+        <v>31</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>73</v>
+      </c>
+      <c r="R31" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1377,6 +1921,26 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>119</v>
+      </c>
+      <c r="N32" t="n">
+        <v>31</v>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1407,6 +1971,26 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>174</v>
+      </c>
+      <c r="N33" t="n">
+        <v>31</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
